--- a/hypersync-results/dr_comparison_hypersync.xlsx
+++ b/hypersync-results/dr_comparison_hypersync.xlsx
@@ -17511,51 +17511,21 @@
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
-      <c r="D127" t="n">
-        <v>300.81</v>
-      </c>
-      <c r="E127" t="n">
-        <v>197.7</v>
-      </c>
-      <c r="F127" t="n">
-        <v>156.26</v>
-      </c>
-      <c r="G127" t="n">
-        <v>154.44</v>
-      </c>
-      <c r="H127" t="n">
-        <v>149.32</v>
-      </c>
-      <c r="I127" t="n">
-        <v>138.39</v>
-      </c>
-      <c r="J127" t="n">
-        <v>16.73</v>
-      </c>
-      <c r="K127" t="n">
-        <v>10.02</v>
-      </c>
-      <c r="L127" t="n">
-        <v>8.970000000000001</v>
-      </c>
-      <c r="M127" t="n">
-        <v>8.91</v>
-      </c>
-      <c r="N127" t="n">
-        <v>8.94</v>
-      </c>
-      <c r="O127" t="n">
-        <v>4.38</v>
-      </c>
-      <c r="P127" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="Q127" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="R127" t="n">
-        <v>0.33</v>
-      </c>
+      <c r="D127" t="inlineStr"/>
+      <c r="E127" t="inlineStr"/>
+      <c r="F127" t="inlineStr"/>
+      <c r="G127" t="inlineStr"/>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
+      <c r="J127" t="inlineStr"/>
+      <c r="K127" t="inlineStr"/>
+      <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
+      <c r="P127" t="inlineStr"/>
+      <c r="Q127" t="inlineStr"/>
+      <c r="R127" t="inlineStr"/>
       <c r="S127" t="n">
         <v>0.33</v>
       </c>
@@ -17581,7 +17551,7 @@
         <v>12492.55</v>
       </c>
       <c r="AA127" t="n">
-        <v>28896.09</v>
+        <v>27740.24</v>
       </c>
       <c r="AB127" t="inlineStr">
         <is>
@@ -21169,7 +21139,7 @@
         <v>27740.24</v>
       </c>
       <c r="M42" t="n">
-        <v>1155.86</v>
+        <v>0</v>
       </c>
       <c r="N42" t="inlineStr">
         <is>
@@ -22170,7 +22140,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E39"/>
+  <dimension ref="A1:E24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -22203,7 +22173,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2024-10</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -22215,37 +22185,37 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>300.8080383671237</v>
+        <v>0.3318514472871808</v>
       </c>
       <c r="E2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>2024-11</t>
+          <t>2026-01</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_risk_capital</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>197.7048212854454</v>
+        <v>177.6857204469182</v>
       </c>
       <c r="E3" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2024-12</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -22257,58 +22227,58 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>156.2640116915537</v>
+        <v>0.3329049989406912</v>
       </c>
       <c r="E4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2025-01</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_flagship</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>154.4372667803067</v>
+        <v>8.620555888252163e-05</v>
       </c>
       <c r="E5" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2025-02</t>
+          <t>2026-02</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_risk_capital</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>149.3197237671313</v>
+        <v>307.7580186696092</v>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2025-03</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B7" t="n">
@@ -22320,58 +22290,58 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>138.3937724247048</v>
+        <v>0.3339434963263763</v>
       </c>
       <c r="E7" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2025-04</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_flagship</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.72518800773313</v>
+        <v>5425.078324149193</v>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>2025-05</t>
+          <t>2026-03</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_risk_capital</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>10.02323501821356</v>
+        <v>147.2736416787795</v>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2025-06</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B10" t="n">
@@ -22383,58 +22353,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>8.967148419076839</v>
+        <v>0.3349734848324279</v>
       </c>
       <c r="E10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2025-07</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_flagship</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>8.912793568136445</v>
+        <v>6454.40020769498</v>
       </c>
       <c r="E11" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>2025-08</t>
+          <t>2026-04</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_risk_capital</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>8.937364988654359</v>
+        <v>26.59639852146469</v>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2025-09</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -22446,58 +22416,58 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.376165615994683</v>
+        <v>1.514372319701787</v>
       </c>
       <c r="E13" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>2025-10</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_flagship</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>0.3286696536304232</v>
+        <v>7020.719853450289</v>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>2025-11</t>
+          <t>2026-05</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1997</v>
+        <v>1999</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_risk_capital</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>0.3295678089045515</v>
+        <v>30.34189158796749</v>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2025-12</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B16" t="n">
@@ -22509,28 +22479,28 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>0.330739718172114</v>
+        <v>6953.518137125108</v>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>skybase_pendle</t>
+          <t>skybase_flagship</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>0.3318514472871808</v>
+        <v>4810.914277181574</v>
       </c>
       <c r="E17" t="b">
         <v>1</v>
@@ -22539,7 +22509,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>2026-01</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="B18" t="n">
@@ -22551,7 +22521,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>177.6857204469182</v>
+        <v>20.23617948770795</v>
       </c>
       <c r="E18" t="b">
         <v>1</v>
@@ -22560,7 +22530,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B19" t="n">
@@ -22572,7 +22542,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>0.3329049989406912</v>
+        <v>8291.323682686629</v>
       </c>
       <c r="E19" t="b">
         <v>1</v>
@@ -22581,7 +22551,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B20" t="n">
@@ -22593,7 +22563,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>8.620555888252163e-05</v>
+        <v>4923.134510263595</v>
       </c>
       <c r="E20" t="b">
         <v>1</v>
@@ -22602,7 +22572,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>2026-02</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="B21" t="n">
@@ -22614,7 +22584,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>307.7580186696092</v>
+        <v>21.14386762725331</v>
       </c>
       <c r="E21" t="b">
         <v>1</v>
@@ -22623,7 +22593,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B22" t="n">
@@ -22635,7 +22605,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3339434963263763</v>
+        <v>12492.54544984775</v>
       </c>
       <c r="E22" t="b">
         <v>1</v>
@@ -22644,7 +22614,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B23" t="n">
@@ -22656,7 +22626,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>5425.078324149193</v>
+        <v>5594.92538693962</v>
       </c>
       <c r="E23" t="b">
         <v>1</v>
@@ -22665,7 +22635,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>2026-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="B24" t="n">
@@ -22677,324 +22647,9 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>147.2736416787795</v>
+        <v>27.71695008796137</v>
       </c>
       <c r="E24" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>skybase_pendle</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>0.3349734848324279</v>
-      </c>
-      <c r="E25" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>skybase_flagship</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>6454.40020769498</v>
-      </c>
-      <c r="E26" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>2026-04</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>skybase_risk_capital</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>26.59639852146469</v>
-      </c>
-      <c r="E27" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>skybase_pendle</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>1.514372319701787</v>
-      </c>
-      <c r="E28" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>skybase_flagship</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>7020.719853450289</v>
-      </c>
-      <c r="E29" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>2026-05</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>skybase_risk_capital</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>30.34189158796749</v>
-      </c>
-      <c r="E30" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>skybase_pendle</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>6953.518137125108</v>
-      </c>
-      <c r="E31" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>skybase_flagship</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>4810.914277181574</v>
-      </c>
-      <c r="E32" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>2026-06</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>skybase_risk_capital</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>20.23617948770795</v>
-      </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>skybase_pendle</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>8291.323682686629</v>
-      </c>
-      <c r="E34" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>skybase_flagship</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>4923.134510263595</v>
-      </c>
-      <c r="E35" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>2026-07</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>skybase_risk_capital</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>21.14386762725331</v>
-      </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1997</v>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>skybase_pendle</t>
-        </is>
-      </c>
-      <c r="D37" t="n">
-        <v>12492.54544984775</v>
-      </c>
-      <c r="E37" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>1998</v>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>skybase_flagship</t>
-        </is>
-      </c>
-      <c r="D38" t="n">
-        <v>5594.92538693962</v>
-      </c>
-      <c r="E38" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>1999</v>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>skybase_risk_capital</t>
-        </is>
-      </c>
-      <c r="D39" t="n">
-        <v>27.71695008796137</v>
-      </c>
-      <c r="E39" t="b">
         <v>1</v>
       </c>
     </row>
